--- a/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:16:44+00:00</t>
+    <t>2025-02-11T12:34:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -473,10 +473,7 @@
   </si>
   <si>
     <t>typeBAL : Type de boîte aux lettres.
-Valeurs possibles :
-ORG pour une BAL organisationnelle;
-APP pour une BAL applicative;
-PER pour une BAL personnelle, rattachée à une personne physique</t>
+Valeurs possibles : ORG | APP | PER | CAB</t>
   </si>
   <si>
     <t>ContactPoint.extension:as-mailbox-mss-metadata.extension:type.id</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:34:01+00:00</t>
+    <t>2025-02-11T13:39:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:39:54+00:00</t>
+    <t>2025-02-11T16:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:00:38+00:00</t>
+    <t>2025-02-11T16:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:22:40+00:00</t>
+    <t>2025-02-12T08:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T08:22:12+00:00</t>
+    <t>2025-02-12T08:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T08:44:28+00:00</t>
+    <t>2025-02-12T08:52:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
